--- a/exports/sobreaviso/escala_geral_sobreaviso_20260721_20260820.xlsx
+++ b/exports/sobreaviso/escala_geral_sobreaviso_20260721_20260820.xlsx
@@ -10,8 +10,8 @@
     <sheet name="ESCALA GERAL" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ESCALA GERAL'!$A$5:$AJ$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'ESCALA GERAL'!$A$1:$AJ$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ESCALA GERAL'!$A$5:$AI$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'ESCALA GERAL'!$A$1:$AI$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,9 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.00&quot; h&quot;"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="11">
     <font>
       <name val="Calibri"/>
@@ -156,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -191,7 +189,6 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -568,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AJ36"/>
+  <dimension ref="A1:AI36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -606,7 +603,6 @@
     <col width="11" customWidth="1" min="33" max="33"/>
     <col width="11" customWidth="1" min="34" max="34"/>
     <col width="11" customWidth="1" min="35" max="35"/>
-    <col width="10" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1" ht="27" customHeight="1">
@@ -840,12 +836,6 @@
         <is>
           <t>20/08
 QUI</t>
-        </is>
-      </c>
-      <c r="AJ5" s="5" t="inlineStr">
-        <is>
-          <t>Total
-horas</t>
         </is>
       </c>
     </row>
@@ -901,21 +891,18 @@
       <c r="AG6" s="10" t="inlineStr"/>
       <c r="AH6" s="10" t="inlineStr"/>
       <c r="AI6" s="10" t="inlineStr"/>
-      <c r="AJ6" s="12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>OBSERVACOES:</t>
         </is>
       </c>
     </row>
     <row r="8" ht="27" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>1 - Horarios apresentados conforme os registros aprovados, pendentes ou planejados do sistema. 2 - Registros cancelados e reprovados nao integram esta escala. 3 - O total considera apenas o trecho dentro da competencia selecionada.</t>
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>1 - Horarios apresentados conforme os registros aprovados, pendentes ou planejados do sistema. 2 - Registros cancelados e reprovados nao integram esta escala.</t>
         </is>
       </c>
     </row>
@@ -1133,66 +1120,59 @@
 QUI</t>
         </is>
       </c>
-      <c r="AJ11" s="5" t="inlineStr">
-        <is>
-          <t>Total
-horas</t>
-        </is>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Nenhum colaborador ativo vinculado a esta subestacao</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
-      <c r="G12" s="16" t="n"/>
-      <c r="H12" s="16" t="n"/>
-      <c r="I12" s="16" t="n"/>
-      <c r="J12" s="16" t="n"/>
-      <c r="K12" s="16" t="n"/>
-      <c r="L12" s="16" t="n"/>
-      <c r="M12" s="16" t="n"/>
-      <c r="N12" s="16" t="n"/>
-      <c r="O12" s="16" t="n"/>
-      <c r="P12" s="16" t="n"/>
-      <c r="Q12" s="16" t="n"/>
-      <c r="R12" s="16" t="n"/>
-      <c r="S12" s="16" t="n"/>
-      <c r="T12" s="16" t="n"/>
-      <c r="U12" s="16" t="n"/>
-      <c r="V12" s="16" t="n"/>
-      <c r="W12" s="16" t="n"/>
-      <c r="X12" s="16" t="n"/>
-      <c r="Y12" s="16" t="n"/>
-      <c r="Z12" s="16" t="n"/>
-      <c r="AA12" s="16" t="n"/>
-      <c r="AB12" s="16" t="n"/>
-      <c r="AC12" s="16" t="n"/>
-      <c r="AD12" s="16" t="n"/>
-      <c r="AE12" s="16" t="n"/>
-      <c r="AF12" s="16" t="n"/>
-      <c r="AG12" s="16" t="n"/>
-      <c r="AH12" s="16" t="n"/>
-      <c r="AI12" s="16" t="n"/>
-      <c r="AJ12" s="16" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="15" t="n"/>
+      <c r="H12" s="15" t="n"/>
+      <c r="I12" s="15" t="n"/>
+      <c r="J12" s="15" t="n"/>
+      <c r="K12" s="15" t="n"/>
+      <c r="L12" s="15" t="n"/>
+      <c r="M12" s="15" t="n"/>
+      <c r="N12" s="15" t="n"/>
+      <c r="O12" s="15" t="n"/>
+      <c r="P12" s="15" t="n"/>
+      <c r="Q12" s="15" t="n"/>
+      <c r="R12" s="15" t="n"/>
+      <c r="S12" s="15" t="n"/>
+      <c r="T12" s="15" t="n"/>
+      <c r="U12" s="15" t="n"/>
+      <c r="V12" s="15" t="n"/>
+      <c r="W12" s="15" t="n"/>
+      <c r="X12" s="15" t="n"/>
+      <c r="Y12" s="15" t="n"/>
+      <c r="Z12" s="15" t="n"/>
+      <c r="AA12" s="15" t="n"/>
+      <c r="AB12" s="15" t="n"/>
+      <c r="AC12" s="15" t="n"/>
+      <c r="AD12" s="15" t="n"/>
+      <c r="AE12" s="15" t="n"/>
+      <c r="AF12" s="15" t="n"/>
+      <c r="AG12" s="15" t="n"/>
+      <c r="AH12" s="15" t="n"/>
+      <c r="AI12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>OBSERVACOES:</t>
         </is>
       </c>
     </row>
     <row r="14" ht="27" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>1 - Horarios apresentados conforme os registros aprovados, pendentes ou planejados do sistema. 2 - Registros cancelados e reprovados nao integram esta escala. 3 - O total considera apenas o trecho dentro da competencia selecionada.</t>
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>1 - Horarios apresentados conforme os registros aprovados, pendentes ou planejados do sistema. 2 - Registros cancelados e reprovados nao integram esta escala.</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1390,6 @@
 QUI</t>
         </is>
       </c>
-      <c r="AJ17" s="5" t="inlineStr">
-        <is>
-          <t>Total
-horas</t>
-        </is>
-      </c>
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
@@ -1438,16 +1412,8 @@
           <t>Operacao</t>
         </is>
       </c>
-      <c r="E18" s="17" t="inlineStr">
-        <is>
-          <t>18:00-24:00</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr">
-        <is>
-          <t>00:00-06:00</t>
-        </is>
-      </c>
+      <c r="E18" s="10" t="inlineStr"/>
+      <c r="F18" s="10" t="inlineStr"/>
       <c r="G18" s="10" t="inlineStr"/>
       <c r="H18" s="10" t="inlineStr"/>
       <c r="I18" s="11" t="inlineStr"/>
@@ -1477,9 +1443,6 @@
       <c r="AG18" s="10" t="inlineStr"/>
       <c r="AH18" s="10" t="inlineStr"/>
       <c r="AI18" s="10" t="inlineStr"/>
-      <c r="AJ18" s="12" t="n">
-        <v>12</v>
-      </c>
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
@@ -1533,9 +1496,6 @@
       <c r="AG19" s="10" t="inlineStr"/>
       <c r="AH19" s="10" t="inlineStr"/>
       <c r="AI19" s="10" t="inlineStr"/>
-      <c r="AJ19" s="12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
@@ -1589,21 +1549,18 @@
       <c r="AG20" s="10" t="inlineStr"/>
       <c r="AH20" s="10" t="inlineStr"/>
       <c r="AI20" s="10" t="inlineStr"/>
-      <c r="AJ20" s="12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>OBSERVACOES:</t>
         </is>
       </c>
     </row>
     <row r="22" ht="27" customHeight="1">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>1 - Horarios apresentados conforme os registros aprovados, pendentes ou planejados do sistema. 2 - Registros cancelados e reprovados nao integram esta escala. 3 - O total considera apenas o trecho dentro da competencia selecionada.</t>
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>1 - Horarios apresentados conforme os registros aprovados, pendentes ou planejados do sistema. 2 - Registros cancelados e reprovados nao integram esta escala.</t>
         </is>
       </c>
     </row>
@@ -1819,12 +1776,6 @@
         <is>
           <t>20/08
 QUI</t>
-        </is>
-      </c>
-      <c r="AJ25" s="5" t="inlineStr">
-        <is>
-          <t>Total
-horas</t>
         </is>
       </c>
     </row>
@@ -1859,10 +1810,28 @@
       <c r="L26" s="10" t="inlineStr"/>
       <c r="M26" s="10" t="inlineStr"/>
       <c r="N26" s="10" t="inlineStr"/>
-      <c r="O26" s="10" t="inlineStr"/>
-      <c r="P26" s="11" t="inlineStr"/>
-      <c r="Q26" s="11" t="inlineStr"/>
-      <c r="R26" s="10" t="inlineStr"/>
+      <c r="O26" s="16" t="inlineStr">
+        <is>
+          <t>16:00-24:00</t>
+        </is>
+      </c>
+      <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>00:00-09:00
+12:00-24:00</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>00:00-12:00
+16:00-24:00</t>
+        </is>
+      </c>
+      <c r="R26" s="16" t="inlineStr">
+        <is>
+          <t>00:00-07:00</t>
+        </is>
+      </c>
       <c r="S26" s="10" t="inlineStr"/>
       <c r="T26" s="10" t="inlineStr"/>
       <c r="U26" s="10" t="inlineStr"/>
@@ -1880,9 +1849,6 @@
       <c r="AG26" s="10" t="inlineStr"/>
       <c r="AH26" s="10" t="inlineStr"/>
       <c r="AI26" s="10" t="inlineStr"/>
-      <c r="AJ26" s="12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="27" ht="26" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
@@ -1908,10 +1874,26 @@
       <c r="E27" s="10" t="inlineStr"/>
       <c r="F27" s="10" t="inlineStr"/>
       <c r="G27" s="10" t="inlineStr"/>
-      <c r="H27" s="10" t="inlineStr"/>
-      <c r="I27" s="11" t="inlineStr"/>
-      <c r="J27" s="11" t="inlineStr"/>
-      <c r="K27" s="10" t="inlineStr"/>
+      <c r="H27" s="16" t="inlineStr">
+        <is>
+          <t>16:00-24:00</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>00:00-24:00</t>
+        </is>
+      </c>
+      <c r="K27" s="16" t="inlineStr">
+        <is>
+          <t>00:00-07:00</t>
+        </is>
+      </c>
       <c r="L27" s="10" t="inlineStr"/>
       <c r="M27" s="10" t="inlineStr"/>
       <c r="N27" s="10" t="inlineStr"/>
@@ -1936,21 +1918,18 @@
       <c r="AG27" s="10" t="inlineStr"/>
       <c r="AH27" s="10" t="inlineStr"/>
       <c r="AI27" s="10" t="inlineStr"/>
-      <c r="AJ27" s="12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>OBSERVACOES:</t>
         </is>
       </c>
     </row>
     <row r="29" ht="27" customHeight="1">
-      <c r="A29" s="14" t="inlineStr">
-        <is>
-          <t>1 - Horarios apresentados conforme os registros aprovados, pendentes ou planejados do sistema. 2 - Registros cancelados e reprovados nao integram esta escala. 3 - O total considera apenas o trecho dentro da competencia selecionada.</t>
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>1 - Horarios apresentados conforme os registros aprovados, pendentes ou planejados do sistema. 2 - Registros cancelados e reprovados nao integram esta escala.</t>
         </is>
       </c>
     </row>
@@ -2166,12 +2145,6 @@
         <is>
           <t>20/08
 QUI</t>
-        </is>
-      </c>
-      <c r="AJ32" s="5" t="inlineStr">
-        <is>
-          <t>Total
-horas</t>
         </is>
       </c>
     </row>
@@ -2227,9 +2200,6 @@
       <c r="AG33" s="10" t="inlineStr"/>
       <c r="AH33" s="10" t="inlineStr"/>
       <c r="AI33" s="10" t="inlineStr"/>
-      <c r="AJ33" s="12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
@@ -2283,46 +2253,43 @@
       <c r="AG34" s="10" t="inlineStr"/>
       <c r="AH34" s="10" t="inlineStr"/>
       <c r="AI34" s="10" t="inlineStr"/>
-      <c r="AJ34" s="12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>OBSERVACOES:</t>
         </is>
       </c>
     </row>
     <row r="36" ht="27" customHeight="1">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>1 - Horarios apresentados conforme os registros aprovados, pendentes ou planejados do sistema. 2 - Registros cancelados e reprovados nao integram esta escala. 3 - O total considera apenas o trecho dentro da competencia selecionada.</t>
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>1 - Horarios apresentados conforme os registros aprovados, pendentes ou planejados do sistema. 2 - Registros cancelados e reprovados nao integram esta escala.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:AJ5"/>
+  <autoFilter ref="A5:AI5"/>
   <mergeCells count="19">
-    <mergeCell ref="A36:AJ36"/>
-    <mergeCell ref="A7:AJ7"/>
-    <mergeCell ref="D2:AJ2"/>
-    <mergeCell ref="A16:AJ16"/>
+    <mergeCell ref="A10:AI10"/>
+    <mergeCell ref="A28:AI28"/>
+    <mergeCell ref="A13:AI13"/>
+    <mergeCell ref="A31:AI31"/>
+    <mergeCell ref="A24:AI24"/>
+    <mergeCell ref="D1:AI1"/>
+    <mergeCell ref="A36:AI36"/>
     <mergeCell ref="A1:C2"/>
-    <mergeCell ref="A21:AJ21"/>
-    <mergeCell ref="A8:AJ8"/>
-    <mergeCell ref="A14:AJ14"/>
-    <mergeCell ref="A22:AJ22"/>
-    <mergeCell ref="A29:AJ29"/>
-    <mergeCell ref="A4:AJ4"/>
-    <mergeCell ref="A35:AJ35"/>
-    <mergeCell ref="A10:AJ10"/>
-    <mergeCell ref="A28:AJ28"/>
-    <mergeCell ref="A13:AJ13"/>
-    <mergeCell ref="A31:AJ31"/>
+    <mergeCell ref="A16:AI16"/>
+    <mergeCell ref="A7:AI7"/>
+    <mergeCell ref="D2:AI2"/>
+    <mergeCell ref="A21:AI21"/>
     <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A24:AJ24"/>
-    <mergeCell ref="D1:AJ1"/>
+    <mergeCell ref="A14:AI14"/>
+    <mergeCell ref="A8:AI8"/>
+    <mergeCell ref="A22:AI22"/>
+    <mergeCell ref="A35:AI35"/>
+    <mergeCell ref="A4:AI4"/>
+    <mergeCell ref="A29:AI29"/>
   </mergeCells>
   <pageMargins left="0.2" right="0.2" top="0.35" bottom="0.35" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
